--- a/public/data/GovStack Global .xlsx
+++ b/public/data/GovStack Global .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ituint-my.sharepoint.com/personal/jody_van_itu_int/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAA25EAF-4D17-47C6-BA9E-75C153DE3647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{073828CD-C16B-4030-8EF1-272497A6BC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-5175" windowWidth="29040" windowHeight="15720" xr2:uid="{1EA68D9A-F93E-4A67-9096-DC39388C24AD}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="463">
   <si>
     <t>Region</t>
   </si>
@@ -286,7 +286,7 @@
     <t>Montenegro</t>
   </si>
   <si>
-    <t>including 10 municipalities</t>
+    <t>Capacity Building  - 10 municipalities</t>
   </si>
   <si>
     <t>Valentina Stadnic</t>
@@ -339,10 +339,7 @@
     <t>Bogata: Govstack Value Proposition Workshop, Citizen Satisfaction Survey Building Block was supported in scoping</t>
   </si>
   <si>
-    <t>cameroon</t>
-  </si>
-  <si>
-    <t>Introdcution</t>
+    <t>Cameroon</t>
   </si>
   <si>
     <t>Name</t>
@@ -363,6 +360,9 @@
     <t>emmanuel.niyikora@itu.int</t>
   </si>
   <si>
+    <t>Senegal</t>
+  </si>
+  <si>
     <t>christine.sund@itu.int</t>
   </si>
   <si>
@@ -375,6 +375,9 @@
     <t>Ashish.Narayan@itu.int</t>
   </si>
   <si>
+    <t>Bangkok</t>
+  </si>
+  <si>
     <t>farid.nakhli@itu.int</t>
   </si>
   <si>
@@ -438,6 +441,9 @@
     <t>Aleksander Reitsakas</t>
   </si>
   <si>
+    <t>Working Group Lead for Information Mediator BB Tech Specs</t>
+  </si>
+  <si>
     <t>Business strategy</t>
   </si>
   <si>
@@ -459,7 +465,7 @@
     <t>Mauree, Venkatesan(Vijay)</t>
   </si>
   <si>
-    <t>Working Group Lead for Payment BB Tech Spec</t>
+    <t>Working Group Lead for Payment BB Tech Specs</t>
   </si>
   <si>
     <t>Telecom, DPI</t>
@@ -471,6 +477,9 @@
     <t>Martin Karner</t>
   </si>
   <si>
+    <t>Working Group Lead for Messaging BB Tech Specs</t>
+  </si>
+  <si>
     <t>DPI, AI &amp; Robotics</t>
   </si>
   <si>
@@ -492,135 +501,144 @@
     <t>Ain Aaviksoo</t>
   </si>
   <si>
+    <t>Working Group Lead for Consent BB Tech Specs</t>
+  </si>
+  <si>
     <t>healthcare innovation and digital transformation</t>
   </si>
   <si>
     <t>https://www.linkedin.com/in/ainaaviksoo/</t>
   </si>
   <si>
+    <t>Tambet artma</t>
+  </si>
+  <si>
+    <t>Registries BB Tech Specs</t>
+  </si>
+  <si>
+    <t>e-governance solutions</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tambetartma/</t>
+  </si>
+  <si>
+    <t>Arnold Kibuuka</t>
+  </si>
+  <si>
+    <t>Payment BB Tech Spec</t>
+  </si>
+  <si>
+    <t>Digital Financial Services</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/arnold-kibuuka/</t>
+  </si>
+  <si>
+    <t>Aare Laponin</t>
+  </si>
+  <si>
+    <t>Workflow BB Tech Specs</t>
+  </si>
+  <si>
+    <t>e-Government services development</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/aarelaponin/</t>
+  </si>
+  <si>
+    <t>Farai mutero</t>
+  </si>
+  <si>
+    <t>Digital health</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/faraimuteroza/</t>
+  </si>
+  <si>
+    <t>Bramhanand Jha</t>
+  </si>
+  <si>
+    <t>Messaging BB Tech Specs</t>
+  </si>
+  <si>
+    <t>eGovernance</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/bramhanand-jha-pmp-0978a129/</t>
+  </si>
+  <si>
+    <t>Satyajit Suri</t>
+  </si>
+  <si>
+    <t>Identity BB Tech Specs</t>
+  </si>
+  <si>
+    <t>Digital Identity | Digital Public Infrastructure | Digital Government</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/satyajitsuri/</t>
+  </si>
+  <si>
+    <t>Lal Chandran</t>
+  </si>
+  <si>
+    <t>Consent BB Tech Spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital Identity  |  eIDAS 2.0  |  EUDI Wallet </t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lalchandran/</t>
+  </si>
+  <si>
+    <t>Benjamin</t>
+  </si>
+  <si>
+    <t>Philippe Page</t>
+  </si>
+  <si>
+    <t>Consent BB Tech Specs</t>
+  </si>
+  <si>
+    <t>Maksim Ovtsinnikov</t>
+  </si>
+  <si>
+    <t>E-governance, interoperability and digital transformation expert</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/maksim-ovtsinnikov/</t>
+  </si>
+  <si>
+    <t>Tarek Rashed</t>
+  </si>
+  <si>
+    <t>Working Group lead for GIS BB Tech Spec</t>
+  </si>
+  <si>
+    <t>Dr.Ramkumar permachanahalli</t>
+  </si>
+  <si>
+    <t>Working Group Lead for Scheduler BB Tech Specs</t>
+  </si>
+  <si>
+    <t>ICT transformation, e-governance</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/dr-ramkumar-permachanahalli-5100648a/</t>
+  </si>
+  <si>
+    <t>Marushka Chocobar</t>
+  </si>
+  <si>
+    <t>AI Governance &amp; Digital Public Infrastructure</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/marushkachocobar/</t>
+  </si>
+  <si>
     <t>Max Carlson (Sandbox)</t>
   </si>
   <si>
-    <t>Tambet artma</t>
-  </si>
-  <si>
-    <t>e-governance solutions</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/tambetartma/</t>
-  </si>
-  <si>
-    <t>James Daley</t>
-  </si>
-  <si>
-    <t>Oscar Correira</t>
-  </si>
-  <si>
-    <t>Information technology, digital finance</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/oscarcorreia/</t>
-  </si>
-  <si>
-    <t>Arnold Kibuuka</t>
-  </si>
-  <si>
-    <t>Payment BB Tech Spec</t>
-  </si>
-  <si>
-    <t>Digital Financial Services</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/arnold-kibuuka/</t>
-  </si>
-  <si>
-    <t>Aare Laponin</t>
-  </si>
-  <si>
-    <t>e-Government services development</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/aarelaponin/</t>
-  </si>
-  <si>
-    <t>Farai mutero</t>
-  </si>
-  <si>
-    <t>Digital health</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/faraimuteroza/</t>
-  </si>
-  <si>
-    <t>Bramhanand Jha</t>
-  </si>
-  <si>
-    <t>eGovernance</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/bramhanand-jha-pmp-0978a129/</t>
-  </si>
-  <si>
-    <t>Satyajit Suri</t>
-  </si>
-  <si>
-    <t>Digital Identity | Digital Public Infrastructure | Digital Government</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/satyajitsuri/</t>
-  </si>
-  <si>
-    <t>Lal Chandran</t>
-  </si>
-  <si>
-    <t>Consent BB Tech Spec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Identity  |  eIDAS 2.0  |  EUDI Wallet </t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/lalchandran/</t>
-  </si>
-  <si>
-    <t>Benjamin</t>
-  </si>
-  <si>
-    <t>Philippe Page</t>
-  </si>
-  <si>
-    <t>Maksim Ovtsinnikov</t>
-  </si>
-  <si>
-    <t>E-governance, interoperability and digital transformation expert</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/maksim-ovtsinnikov/</t>
-  </si>
-  <si>
-    <t>Tarek Rashed</t>
-  </si>
-  <si>
-    <t>Working Group lead for GIS BB Tech Spec</t>
-  </si>
-  <si>
-    <t>Marushka Chocobar</t>
-  </si>
-  <si>
-    <t>AI Governance &amp; Digital Public Infrastructure</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/marushkachocobar/</t>
-  </si>
-  <si>
-    <t>Dr.Ramkumar permachanahalli</t>
-  </si>
-  <si>
-    <t>ICT transformation, e-governance</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/dr-ramkumar-permachanahalli-5100648a/</t>
-  </si>
-  <si>
     <t>Asset</t>
   </si>
   <si>
@@ -1032,9 +1050,6 @@
     <t>Cabo Verde</t>
   </si>
   <si>
-    <t>Cameroon</t>
-  </si>
-  <si>
     <t>Canada</t>
   </si>
   <si>
@@ -1345,9 +1360,6 @@
   </si>
   <si>
     <t>Saudi Arabia</t>
-  </si>
-  <si>
-    <t>Senegal</t>
   </si>
   <si>
     <t>Seychelles</t>
@@ -2416,7 +2428,6 @@
       <c r="G3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
@@ -3024,7 +3035,7 @@
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" ht="15">
       <c r="B32" s="4" t="s">
         <v>66</v>
       </c>
@@ -3037,8 +3048,8 @@
       <c r="E32" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>21</v>
+      <c r="F32" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>69</v>
@@ -3073,8 +3084,8 @@
       <c r="D34" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>83</v>
+      <c r="E34" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>25</v>
@@ -7931,7 +7942,7 @@
           <x14:formula1>
             <xm:f>'Input Sheet'!$D$2:$D$4</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F29 F34</xm:sqref>
+          <xm:sqref>F2:F29 F34 F32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9C9EFD4E-5484-43C0-BC45-7382A08B71E6}">
           <x14:formula1>
@@ -7943,7 +7954,7 @@
           <x14:formula1>
             <xm:f>'Focal Points'!$B$2:$B$10</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:I997</xm:sqref>
+          <xm:sqref>G2:G997 I2:I997 H2 H4:H997</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7967,13 +7978,13 @@
         <v>Region</v>
       </c>
       <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>85</v>
-      </c>
-      <c r="D1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7985,10 +7996,10 @@
         <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
         <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7999,6 +8010,9 @@
         <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
         <v>89</v>
       </c>
     </row>
@@ -8036,6 +8050,9 @@
       <c r="C6" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="str">
@@ -8046,10 +8063,10 @@
         <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -8061,10 +8078,10 @@
         <v>69</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -8073,27 +8090,27 @@
         <v>Americas</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -8111,7 +8128,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C022A9-E78A-4630-983B-9C49EEA76207}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -8122,270 +8139,290 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="43.5">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29.1">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.5">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="29.1">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="29.1">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>127</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="F6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>135</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>135</v>
+        <v>139</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>143</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="F10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>147</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>151</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F13" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>158</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="F14" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>150</v>
+        <v>162</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="F15" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" t="s">
-        <v>154</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>156</v>
-      </c>
-      <c r="F17" t="s">
-        <v>157</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="F18" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>164</v>
+        <v>172</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29.1">
+      <c r="A20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F20" t="s">
+        <v>176</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>165</v>
+      <c r="A21" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="F21" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>168</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F23" t="s">
-        <v>171</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="29.1">
-      <c r="A24" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F24" t="s">
-        <v>174</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -8397,17 +8434,16 @@
     <hyperlink ref="G6" r:id="rId5" xr:uid="{195A66B4-5CE6-42F1-A732-9FD48A423576}"/>
     <hyperlink ref="G7" r:id="rId6" xr:uid="{09D1A0BA-E2BD-4DE8-B2C0-ECC1B63F1439}"/>
     <hyperlink ref="G8" r:id="rId7" xr:uid="{74DFEACC-13D2-4777-AE92-CBEDDD84978D}"/>
-    <hyperlink ref="G10" r:id="rId8" xr:uid="{434BBFC9-2F01-48ED-A5A1-0FC417C73E59}"/>
-    <hyperlink ref="G12" r:id="rId9" xr:uid="{862A020C-5E06-4FA5-9417-73561D0F9112}"/>
-    <hyperlink ref="G13" r:id="rId10" xr:uid="{A9E4ACAD-A592-49A8-A75A-342B5EA2F04F}"/>
-    <hyperlink ref="G14" r:id="rId11" xr:uid="{825BD7D3-A5BE-42BA-A190-6A28D88EFA81}"/>
-    <hyperlink ref="G15" r:id="rId12" xr:uid="{320F5518-5066-4C9E-8C71-0402E9D3190F}"/>
-    <hyperlink ref="G16" r:id="rId13" xr:uid="{16BEE7D5-CB4C-48D0-A111-0592C822FB19}"/>
-    <hyperlink ref="G17" r:id="rId14" xr:uid="{2122AEFB-D919-46FA-BB1D-5D254E4143E6}"/>
-    <hyperlink ref="G18" r:id="rId15" xr:uid="{477EC803-7E19-45A1-B2F1-7BC2E99B4706}"/>
-    <hyperlink ref="G21" r:id="rId16" xr:uid="{DF72DE48-CC44-48F0-B800-4412BAA48BD0}"/>
-    <hyperlink ref="G24" r:id="rId17" xr:uid="{45E024D9-B5DD-46C5-9C5E-F0882232E57D}"/>
-    <hyperlink ref="G23" r:id="rId18" xr:uid="{23ABDA90-BA78-44F4-925D-28B0D7AF4C1C}"/>
+    <hyperlink ref="G9" r:id="rId8" xr:uid="{434BBFC9-2F01-48ED-A5A1-0FC417C73E59}"/>
+    <hyperlink ref="G10" r:id="rId9" xr:uid="{A9E4ACAD-A592-49A8-A75A-342B5EA2F04F}"/>
+    <hyperlink ref="G11" r:id="rId10" xr:uid="{825BD7D3-A5BE-42BA-A190-6A28D88EFA81}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{320F5518-5066-4C9E-8C71-0402E9D3190F}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{16BEE7D5-CB4C-48D0-A111-0592C822FB19}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{2122AEFB-D919-46FA-BB1D-5D254E4143E6}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{477EC803-7E19-45A1-B2F1-7BC2E99B4706}"/>
+    <hyperlink ref="G18" r:id="rId15" xr:uid="{DF72DE48-CC44-48F0-B800-4412BAA48BD0}"/>
+    <hyperlink ref="G20" r:id="rId16" xr:uid="{45E024D9-B5DD-46C5-9C5E-F0882232E57D}"/>
+    <hyperlink ref="G21" r:id="rId17" xr:uid="{23ABDA90-BA78-44F4-925D-28B0D7AF4C1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8423,407 +8459,407 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="188.45">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="79.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="43.5">
       <c r="A4" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="87">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29.1">
       <c r="A7" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="29.1">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29.1">
       <c r="A9" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="29.1">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29.1">
       <c r="A11" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="43.5">
       <c r="A12" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="29.1">
       <c r="A13" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="29.1">
       <c r="A14" s="2" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="29.1">
       <c r="A15" s="2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="87">
       <c r="A16" s="2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="43.5">
       <c r="A17" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="174">
       <c r="A18" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="43.5">
       <c r="A19" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="43.5">
       <c r="A20" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="43.5">
       <c r="A21" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="188.45">
       <c r="A22" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="203.1">
       <c r="A23" s="2" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="188.45">
       <c r="A24" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -8871,13 +8907,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -8891,16 +8927,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
@@ -8908,13 +8944,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -8923,7 +8959,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8931,16 +8967,16 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8948,13 +8984,13 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8962,10 +8998,10 @@
         <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8973,51 +9009,51 @@
         <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="B10" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -9027,27 +9063,27 @@
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="2:2">
@@ -9057,47 +9093,47 @@
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" spans="2:2">
@@ -9107,32 +9143,32 @@
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>313</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="38" spans="2:2">
@@ -9142,67 +9178,67 @@
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="52" spans="2:2">
@@ -9212,32 +9248,32 @@
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="2:2">
@@ -9247,7 +9283,7 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="61" spans="2:2">
@@ -9257,57 +9293,57 @@
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="2:2">
@@ -9317,77 +9353,77 @@
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="B82" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="B85" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="B88" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -9404,42 +9440,42 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="B90" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="B93" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="B94" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="B95" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="97" spans="2:2">
@@ -9449,62 +9485,62 @@
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="110" spans="2:2">
@@ -9514,22 +9550,22 @@
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="115" spans="2:2">
@@ -9544,7 +9580,7 @@
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="118" spans="2:2">
@@ -9554,17 +9590,17 @@
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="122" spans="2:2">
@@ -9574,42 +9610,42 @@
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="131" spans="2:2">
@@ -9624,7 +9660,7 @@
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="134" spans="2:2">
@@ -9634,72 +9670,72 @@
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="149" spans="2:2">
@@ -9709,22 +9745,22 @@
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>418</v>
+        <v>89</v>
       </c>
     </row>
     <row r="154" spans="2:2">
@@ -9734,122 +9770,122 @@
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="179" spans="2:2">
@@ -9859,47 +9895,47 @@
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="2:2">
@@ -9909,27 +9945,27 @@
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -9952,10 +9988,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9992,7 +10028,7 @@
         <v>60000</v>
       </c>
       <c r="E4" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10033,7 +10069,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="15" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B8">
         <f>SUM(B2:B7)</f>
@@ -10072,6 +10108,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6cd167fc-a253-46cf-a6e8-b2a3895acce7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009840361495D9184DA98268158DDE04CB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54a82e38326b2858f84a6473f4dd4ed1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6cd167fc-a253-46cf-a6e8-b2a3895acce7" xmlns:ns4="5b32c6ad-66c6-4f1d-b199-99e785096fb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e7d14268ea1aaa55747cf34b0c6211e0" ns3:_="" ns4:_="">
     <xsd:import namespace="6cd167fc-a253-46cf-a6e8-b2a3895acce7"/>
@@ -10298,7 +10342,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -10307,22 +10351,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6cd167fc-a253-46cf-a6e8-b2a3895acce7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4798A5DE-CF0A-46C4-8A2B-9F98B2133F89}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D2DB26-1A28-4E75-848E-E3C4499A61D1}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CEA1C9B-312A-4AD1-B745-70D8FB5F97CA}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4798A5DE-CF0A-46C4-8A2B-9F98B2133F89}"/>
 </file>
--- a/public/data/GovStack Global .xlsx
+++ b/public/data/GovStack Global .xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ituint-my.sharepoint.com/personal/jody_van_itu_int/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{073828CD-C16B-4030-8EF1-272497A6BC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F60EAB9D-12A3-4073-8666-B21F4F57241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-5175" windowWidth="29040" windowHeight="15720" xr2:uid="{1EA68D9A-F93E-4A67-9096-DC39388C24AD}"/>
+    <workbookView xWindow="-28920" yWindow="-5175" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1EA68D9A-F93E-4A67-9096-DC39388C24AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Global View" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="465">
   <si>
     <t>Region</t>
   </si>
@@ -135,7 +135,7 @@
     <t>Ashish Narayan</t>
   </si>
   <si>
-    <t>Timor leste (Portugeese)</t>
+    <t>Timor-Leste</t>
   </si>
   <si>
     <t>GovStack general training</t>
@@ -150,7 +150,7 @@
     <t>Digital ID and GovStack training</t>
   </si>
   <si>
-    <t>Lao PDR</t>
+    <t>Lao People's Democratic Republic</t>
   </si>
   <si>
     <t>Training on GovStack whole of government</t>
@@ -174,7 +174,7 @@
     <t>Creating a roadmap for building blocks</t>
   </si>
   <si>
-    <t>BIMSTEC</t>
+    <t>Bangladesh,BIMSTEC</t>
   </si>
   <si>
     <t>Training of trainers online</t>
@@ -268,9 +268,6 @@
     <t>Nakhli, Farid</t>
   </si>
   <si>
-    <t>Laos</t>
-  </si>
-  <si>
     <t>Lesotho</t>
   </si>
   <si>
@@ -366,12 +363,24 @@
     <t>christine.sund@itu.int</t>
   </si>
   <si>
+    <t>Addis Ababa</t>
+  </si>
+  <si>
+    <t>Serge Ndigui</t>
+  </si>
+  <si>
+    <t>serge.yebel@itu.int</t>
+  </si>
+  <si>
     <t>Riham Fahkry</t>
   </si>
   <si>
     <t>riham.fakhry@itu.int</t>
   </si>
   <si>
+    <t>Cairo</t>
+  </si>
+  <si>
     <t>Ashish.Narayan@itu.int</t>
   </si>
   <si>
@@ -396,7 +405,7 @@
     <t>Sergio.Scarabino@itu.int</t>
   </si>
   <si>
-    <t> Santiago</t>
+    <t>Santiago</t>
   </si>
   <si>
     <t>HQ</t>
@@ -1414,9 +1423,6 @@
   </si>
   <si>
     <t>Thailand</t>
-  </si>
-  <si>
-    <t>Timor-Leste</t>
   </si>
   <si>
     <t>Togo</t>
@@ -2431,11 +2437,11 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" ht="15">
       <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="12" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -2842,7 +2848,7 @@
         <v>18</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>13</v>
@@ -2861,7 +2867,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>13</v>
@@ -2880,7 +2886,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>13</v>
@@ -2889,27 +2895,27 @@
         <v>15</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="2:10">
       <c r="B25" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>66</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>67</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -2919,7 +2925,7 @@
         <v>58</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>13</v>
@@ -2928,7 +2934,7 @@
         <v>21</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
@@ -2938,7 +2944,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>13</v>
@@ -2955,7 +2961,7 @@
         <v>11</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>13</v>
@@ -2964,7 +2970,7 @@
         <v>25</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
@@ -2980,7 +2986,7 @@
         <v>13</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>25</v>
@@ -2996,19 +3002,19 @@
         <v>11</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
@@ -3018,26 +3024,26 @@
         <v>11</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>13</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
     </row>
     <row r="32" spans="2:10" ht="15">
       <c r="B32" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>12</v>
@@ -3046,13 +3052,13 @@
         <v>13</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
@@ -3062,13 +3068,13 @@
         <v>54</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -3079,7 +3085,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>13</v>
@@ -7952,9 +7958,9 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C493D269-137C-41E8-B2D6-7D2B520EFD53}">
           <x14:formula1>
-            <xm:f>'Focal Points'!$B$2:$B$10</xm:f>
+            <xm:f>'Focal Points'!$B$2:$B$11</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G997 I2:I997 H2 H4:H997</xm:sqref>
+          <xm:sqref>G2:G997 H4:H997 H2 I2:I997</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7964,12 +7970,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52514E42-12B2-4022-9269-FCEEAC82F2D7}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
     <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -7978,13 +7985,13 @@
         <v>Region</v>
       </c>
       <c r="B1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>84</v>
-      </c>
-      <c r="D1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7996,10 +8003,10 @@
         <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
         <v>86</v>
-      </c>
-      <c r="D2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -8007,13 +8014,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
         <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -8021,105 +8028,125 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" t="str">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="str">
         <f>'Input Sheet'!A3</f>
         <v>Arab States</v>
       </c>
-      <c r="B5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="str">
+      <c r="B6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="str">
         <f>'Input Sheet'!A4</f>
         <v>Asia-Pacific</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="str">
+      <c r="C7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="str">
         <f>'Input Sheet'!A5</f>
         <v>CIS</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="str">
+      <c r="C8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="str">
         <f>'Input Sheet'!A6</f>
         <v>Europe</v>
       </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="str">
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="str">
         <f>'Input Sheet'!A7</f>
         <v>Americas</v>
       </c>
-      <c r="B9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" xr:uid="{515A0CE3-6C1D-4118-B4F7-4620BE6C6186}"/>
-    <hyperlink ref="C6" r:id="rId2" xr:uid="{2C70267B-2ABE-4DE3-9F84-15F213288A0F}"/>
-    <hyperlink ref="C7" r:id="rId3" xr:uid="{D6EFE1F0-9CFD-4FD3-BCA6-270C3AEE5C07}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{DE19EED9-77EF-4207-93B2-BCBE28047501}"/>
-    <hyperlink ref="C8" r:id="rId5" xr:uid="{75E73072-8E1F-4D4A-A080-CB6F366B365F}"/>
+    <hyperlink ref="C11" r:id="rId1" xr:uid="{515A0CE3-6C1D-4118-B4F7-4620BE6C6186}"/>
+    <hyperlink ref="C7" r:id="rId2" xr:uid="{2C70267B-2ABE-4DE3-9F84-15F213288A0F}"/>
+    <hyperlink ref="C8" r:id="rId3" xr:uid="{D6EFE1F0-9CFD-4FD3-BCA6-270C3AEE5C07}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{DE19EED9-77EF-4207-93B2-BCBE28047501}"/>
+    <hyperlink ref="C9" r:id="rId5" xr:uid="{75E73072-8E1F-4D4A-A080-CB6F366B365F}"/>
     <hyperlink ref="C2" r:id="rId6" xr:uid="{D19818F0-5E2A-451B-BF4F-54BD75F3D891}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8139,290 +8166,290 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.1">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="29.1">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="29.1">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F15" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="29.1">
       <c r="A20" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F20" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F21" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -8459,407 +8486,407 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="188.45">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="79.5" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="43.5">
       <c r="A4" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="43.5">
       <c r="A5" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="87">
       <c r="A6" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="29.1">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="29.1">
       <c r="A8" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="29.1">
       <c r="A9" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="29.1">
       <c r="A10" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="29.1">
       <c r="A11" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="43.5">
       <c r="A12" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="29.1">
       <c r="A13" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="29.1">
       <c r="A14" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="29.1">
       <c r="A15" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="87">
       <c r="A16" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="43.5">
       <c r="A17" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="174">
       <c r="A18" s="2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="43.5">
       <c r="A19" s="2" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="43.5">
       <c r="A20" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="43.5">
       <c r="A21" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="188.45">
       <c r="A22" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="203.1">
       <c r="A23" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="188.45">
       <c r="A24" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -8907,13 +8934,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
@@ -8927,16 +8954,16 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
@@ -8944,13 +8971,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -8959,7 +8986,7 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8967,16 +8994,16 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8984,24 +9011,24 @@
         <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9009,51 +9036,51 @@
         <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1">
       <c r="B10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="B11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="B12" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="B13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="B14" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -9063,27 +9090,27 @@
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="2:2">
@@ -9093,47 +9120,47 @@
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="2:2">
@@ -9143,102 +9170,102 @@
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="52" spans="2:2">
@@ -9248,32 +9275,32 @@
     </row>
     <row r="53" spans="2:2">
       <c r="B53" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="59" spans="2:2">
@@ -9283,7 +9310,7 @@
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="2:2">
@@ -9293,137 +9320,137 @@
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="2:2">
       <c r="B64" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="B82" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="B85" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="B88" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -9440,132 +9467,132 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="B90" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="B93" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="B94" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="B95" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="97" spans="2:2">
       <c r="B97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" spans="2:2">
       <c r="B98" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="99" spans="2:2">
       <c r="B99" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="100" spans="2:2">
       <c r="B100" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="101" spans="2:2">
       <c r="B101" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="102" spans="2:2">
       <c r="B102" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="103" spans="2:2">
       <c r="B103" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="104" spans="2:2">
       <c r="B104" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="105" spans="2:2">
       <c r="B105" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="106" spans="2:2">
       <c r="B106" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="107" spans="2:2">
       <c r="B107" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="108" spans="2:2">
       <c r="B108" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="109" spans="2:2">
       <c r="B109" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="110" spans="2:2">
       <c r="B110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="111" spans="2:2">
       <c r="B111" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="112" spans="2:2">
       <c r="B112" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="115" spans="2:2">
@@ -9575,32 +9602,32 @@
     </row>
     <row r="116" spans="2:2">
       <c r="B116" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119" spans="2:2">
       <c r="B119" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="120" spans="2:2">
       <c r="B120" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="122" spans="2:2">
@@ -9610,42 +9637,42 @@
     </row>
     <row r="123" spans="2:2">
       <c r="B123" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="2:2">
       <c r="B124" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="2:2">
       <c r="B125" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="126" spans="2:2">
       <c r="B126" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="127" spans="2:2">
       <c r="B127" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="128" spans="2:2">
       <c r="B128" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" spans="2:2">
       <c r="B129" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130" spans="2:2">
       <c r="B130" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="131" spans="2:2">
@@ -9660,7 +9687,7 @@
     </row>
     <row r="133" spans="2:2">
       <c r="B133" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="134" spans="2:2">
@@ -9670,72 +9697,72 @@
     </row>
     <row r="135" spans="2:2">
       <c r="B135" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="136" spans="2:2">
       <c r="B136" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="2:2">
       <c r="B137" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="138" spans="2:2">
       <c r="B138" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="139" spans="2:2">
       <c r="B139" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="140" spans="2:2">
       <c r="B140" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="141" spans="2:2">
       <c r="B141" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="142" spans="2:2">
       <c r="B142" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="143" spans="2:2">
       <c r="B143" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="144" spans="2:2">
       <c r="B144" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="145" spans="2:2">
       <c r="B145" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="146" spans="2:2">
       <c r="B146" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="147" spans="2:2">
       <c r="B147" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="148" spans="2:2">
       <c r="B148" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="149" spans="2:2">
@@ -9745,147 +9772,147 @@
     </row>
     <row r="150" spans="2:2">
       <c r="B150" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="151" spans="2:2">
       <c r="B151" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="152" spans="2:2">
       <c r="B152" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="153" spans="2:2">
       <c r="B153" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="154" spans="2:2">
       <c r="B154" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="155" spans="2:2">
       <c r="B155" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="156" spans="2:2">
       <c r="B156" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="157" spans="2:2">
       <c r="B157" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="2:2">
       <c r="B158" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="159" spans="2:2">
       <c r="B159" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="2:2">
       <c r="B160" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="161" spans="2:2">
       <c r="B161" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="162" spans="2:2">
       <c r="B162" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="163" spans="2:2">
       <c r="B163" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="164" spans="2:2">
       <c r="B164" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="165" spans="2:2">
       <c r="B165" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="2:2">
       <c r="B166" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="167" spans="2:2">
       <c r="B167" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="168" spans="2:2">
       <c r="B168" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="169" spans="2:2">
       <c r="B169" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="170" spans="2:2">
       <c r="B170" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="171" spans="2:2">
       <c r="B171" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="172" spans="2:2">
       <c r="B172" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="173" spans="2:2">
       <c r="B173" t="s">
-        <v>441</v>
+        <v>23</v>
       </c>
     </row>
     <row r="174" spans="2:2">
       <c r="B174" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="2:2">
       <c r="B175" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="2:2">
       <c r="B176" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="2:2">
       <c r="B177" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="2:2">
       <c r="B178" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="2:2">
@@ -9895,47 +9922,47 @@
     </row>
     <row r="180" spans="2:2">
       <c r="B180" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="181" spans="2:2">
       <c r="B181" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="182" spans="2:2">
       <c r="B182" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="183" spans="2:2">
       <c r="B183" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="184" spans="2:2">
       <c r="B184" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="185" spans="2:2">
       <c r="B185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="186" spans="2:2">
       <c r="B186" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="187" spans="2:2">
       <c r="B187" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="188" spans="2:2">
       <c r="B188" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="189" spans="2:2">
@@ -9945,27 +9972,27 @@
     </row>
     <row r="190" spans="2:2">
       <c r="B190" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="2:2">
       <c r="B191" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="2:2">
       <c r="B192" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="193" spans="2:2">
       <c r="B193" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -9988,10 +10015,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10028,7 +10055,7 @@
         <v>60000</v>
       </c>
       <c r="E4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -10064,12 +10091,12 @@
         <v>16500</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="15" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B8">
         <f>SUM(B2:B7)</f>

--- a/public/data/GovStack Global .xlsx
+++ b/public/data/GovStack Global .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ituint-my.sharepoint.com/personal/jody_van_itu_int/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F60EAB9D-12A3-4073-8666-B21F4F57241D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9804DA6B-2698-48B9-9544-A65F3DAE6EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-5175" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1EA68D9A-F93E-4A67-9096-DC39388C24AD}"/>
+    <workbookView xWindow="-28920" yWindow="-5175" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{1EA68D9A-F93E-4A67-9096-DC39388C24AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Global View" sheetId="1" r:id="rId1"/>
@@ -657,7 +657,7 @@
     <t>Link</t>
   </si>
   <si>
-    <t>Target Audiance</t>
+    <t>Target Audience</t>
   </si>
   <si>
     <t>PAERA (Public Administration and E-Governance Readiness Assessment)</t>
@@ -705,7 +705,7 @@
     <t>GovStack GitHub Repository</t>
   </si>
   <si>
-    <t>Buildinng Blocks</t>
+    <t>Building Blocks</t>
   </si>
   <si>
     <t>https://github.com/GovStackWorkingGroup</t>
@@ -8484,7 +8484,7 @@
     <col min="1" max="5" width="33.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" ht="15">
       <c r="A1" s="9" t="s">
         <v>185</v>
       </c>
@@ -8586,7 +8586,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="29.1">
+    <row r="7" spans="1:10" ht="29.25">
       <c r="A7" s="2" t="s">
         <v>212</v>
       </c>
@@ -8603,7 +8603,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="29.1">
+    <row r="8" spans="1:10" ht="29.25">
       <c r="A8" s="2" t="s">
         <v>216</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="29.1">
+    <row r="9" spans="1:10" ht="29.25">
       <c r="A9" s="2" t="s">
         <v>220</v>
       </c>
@@ -8637,7 +8637,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="29.1">
+    <row r="10" spans="1:10" ht="43.5">
       <c r="A10" s="2" t="s">
         <v>224</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="29.1">
+    <row r="11" spans="1:10" ht="29.25">
       <c r="A11" s="2" t="s">
         <v>228</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="29.1">
+    <row r="13" spans="1:10" ht="29.25">
       <c r="A13" s="2" t="s">
         <v>235</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="29.1">
+    <row r="14" spans="1:10" ht="29.25">
       <c r="A14" s="2" t="s">
         <v>239</v>
       </c>
@@ -8722,7 +8722,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="29.1">
+    <row r="15" spans="1:10" ht="29.25">
       <c r="A15" s="2" t="s">
         <v>242</v>
       </c>
@@ -10135,6 +10135,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="6cd167fc-a253-46cf-a6e8-b2a3895acce7" xsi:nil="true"/>
@@ -10142,7 +10151,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009840361495D9184DA98268158DDE04CB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54a82e38326b2858f84a6473f4dd4ed1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="6cd167fc-a253-46cf-a6e8-b2a3895acce7" xmlns:ns4="5b32c6ad-66c6-4f1d-b199-99e785096fb2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e7d14268ea1aaa55747cf34b0c6211e0" ns3:_="" ns4:_="">
     <xsd:import namespace="6cd167fc-a253-46cf-a6e8-b2a3895acce7"/>
@@ -10369,23 +10378,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CEA1C9B-312A-4AD1-B745-70D8FB5F97CA}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4798A5DE-CF0A-46C4-8A2B-9F98B2133F89}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25D2DB26-1A28-4E75-848E-E3C4499A61D1}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CEA1C9B-312A-4AD1-B745-70D8FB5F97CA}"/>
 </file>